--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0090.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0090.xlsx
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Dùng game VR để điều chỉnh tần số Cộng Hưởng Giả à? Ý hay đấy.</t>
+          <t>Dùng game VR để điều chỉnh tần số Resonator à? Ý hay đấy.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Tài liệu ta bảo cậu bỏ vào ngăn kéo bàn ta đâu rồi?</t>
+          <t>Tài liệu tao bảo cậu bỏ vào ngăn kéo bàn tao đâu rồi?</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Ừ... được rồi. Lần sau nhớ cho ta biết ngươi cất đồ ở đâu nhé.</t>
+          <t>Ừ... được rồi. Lần sau nhớ cho tao biết mày cất đồ ở đâu nhé.</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Đúng thật đấy! Mỗi lần ta đi học, tim nó lại tan nát. Năng lượng húc đầu của nó giờ đã xuống mức thấp nhất từ trước đến nay…</t>
+          <t>Đúng thật đấy! Mỗi lần tao đi học, tim nó lại tan nát. Năng lượng húc đầu của nó giờ đã xuống mức thấp nhất từ trước đến nay…</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Tin xấu. Mấy cây ở Khu Nông Nghiệp vừa cắn nát dự án luận án của cậu rồi.</t>
+          <t>Tin xấu. Mấy cây ở Khu Nông Nghiệp vừa cắn nát dự án luận án của mày rồi.</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Giờ thì đây là thủ tục tiêu chuẩn rồi... Lần trước ta đọc bản tóm tắt của cậu, tai ta ù suốt ba ngày liền.</t>
+          <t>Giờ thì đây là thủ tục tiêu chuẩn rồi... Lần trước tao đọc bản tóm tắt của cậu, tai tao ù suốt ba ngày liền.</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Bao nhiêu lần ta đã nói rồi—luận văn là công trình gốc, đòi hỏi phải suy nghĩ!</t>
+          <t>Bao nhiêu lần tao đã nói rồi—luận văn là công trình gốc, đòi hỏi phải suy nghĩ!</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Trong bài của cậu có chỗ nào chứng tỏ cậu suy nghĩ không? Tốt nhất đổi tên thành "Bài Tổng Quan Văn Học Của Tôi" cho rồi!</t>
+          <t>Trong bài của mày có chỗ nào chứng tỏ mày suy nghĩ không? Tốt nhất đổi tên thành "Bài Tổng Quan Văn Học Của Tôi" cho rồi!</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Ta phải nói bao nhiêu lần nữa mới được, đó chỉ là hiệu ứng giả dược thôi!</t>
+          <t>Tao phải nói bao nhiêu lần nữa mới được, đó chỉ là hiệu ứng giả dược thôi!</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Nếu vẽ bùa lên người mà có tác dụng thật, thì tại sao Hội Roya lại phải dày công nghiên cứu để tạo ra bùa thật chứ?! Giờ r?i ?i mà lau sạch đi!</t>
+          <t>Nếu vẽ bùa lên người mà có tác dụng thật, thì tại sao Hội Roya lại phải dày công nghiên cứu để tạo ra bùa thật chứ?! Giờ cút đi mà lau sạch đi!</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Số lượng là sức mạnh. Càng nhiều càng tốt! Cậu có biết thẩm mỹ cơ khí là gì không?</t>
+          <t>Số lượng là sức mạnh. Càng nhiều càng tốt! Mày có biết thẩm mỹ cơ khí là gì không?</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Thằng nhóc đó sắp rút khỏi Startorch rồi. Ta không thuyết phục được nó ở lại.</t>
+          <t>Thằng nhóc đó sắp rút khỏi Startorch rồi. Tao không thuyết phục được nó ở lại.</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Áp Lực Ngưỡng... Đúng rồi, ta đang ở đó rồi đây...</t>
+          <t>Áp Lực Ngưỡng... Đúng rồi, tao đang ở đó rồi đây...</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Đừng giả vờ già yếu. Với Cộng Hưởng Giả, cậu vẫn còn trẻ mà!</t>
+          <t>Đừng giả vờ già yếu. Với Resonator, cậu vẫn còn trẻ mà!</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Người Huanglong có câu: "Kẻ bơi giỏi nhất vẫn có thể yếu đuối." Ta thực sự lo lắng cho tụi nó khi ra ngoài vùng băng giá.</t>
+          <t>Người Huanglong có câu: "Kẻ bơi giỏi nhất vẫn có thể yếu đuối." Tao thực sự lo lắng cho tụi nó khi ra ngoài vùng băng giá.</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Lần tới có chuyến thám hiểm, cho tụi nó vào đội ta. Ta sẽ đảm bảo huấn luyện chúng tử tế.</t>
+          <t>Lần tới có chuyến thám hiểm, cho tụi nó vào đội tao. Tao sẽ đảm bảo huấn luyện chúng tử tế.</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Ngoài ra... Nếu cậu muốn nghe ý kiến của ta, ta luôn nói đừng bỏ bữa. Cần năng lượng để giữ đầu óc tỉnh táo ngoài kia mà.</t>
+          <t>Ngoài ra... Nếu cậu muốn nghe ý kiến của tao, tao luôn nói đừng bỏ bữa. Cần năng lượng để giữ đầu óc tỉnh táo ngoài kia mà.</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Ta chỉnh mạch điện một chút rồi nó hỏng. Lại đây giúp ta xem thử!</t>
+          <t>Tao chỉnh mạch điện một chút rồi nó hỏng. Lại đây giúp tao xem thử!</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Ta muốn cậu đưa cả hai đứa chúng nó đi ngay lập tức! Bất cứ đâu cũng được, chỉ đừng ở đây nữa! Ọe... Ta sắp ói mất rồi...</t>
+          <t>Tao muốn cậu đưa cả hai đứa chúng nó đi ngay lập tức! Bất cứ đâu cũng được, chỉ đừng ở đây nữa! Ọe... Tao sắp ói mất rồi...</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Massi! Lâu lắm rồi không gặp ông già khó tính đó. Nghe đây, xóa tên ta khỏi luận văn của ngươi đi. Ghi ông ấy làm người hướng dẫn cho ngươi.</t>
+          <t>Massi! Lâu lắm rồi không gặp ông già khó tính đó. Nghe đây, xóa tên tao khỏi luận văn của mày đi. Ghi ông ấy làm người hướng dẫn cho mày.</t>
         </is>
       </c>
     </row>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Cậu phải tấn công boss từ xa, rồi đổi sang Kiếm để đỡ đòn và phá thế của nó...</t>
+          <t>Cậu phải tấn công boss từ xa, rồi đổi sang Kiếm đơn để đỡ đòn và phá thế của nó...</t>
         </is>
       </c>
     </row>
@@ -31059,7 +31059,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Khó thật đấy, ta biết. Ta đã luyện tập hàng đống thời gian mới làm được. Ngày xưa, mỗi lần thử là lại bị tơi tả…</t>
+          <t>Khó thật đấy, tao biết. Tao đã luyện tập hàng đống thời gian mới làm được. Ngày xưa, mỗi lần thử là lại bị tơi tả…</t>
         </is>
       </c>
     </row>
@@ -32229,7 +32229,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Nào. Đến căng tin thôi. Ta mời bằng thẻ của ta.</t>
+          <t>Nào. Đến căng tin thôi. Tao mời bằng thẻ của tao.</t>
         </is>
       </c>
     </row>
@@ -32359,7 +32359,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>...Cậu có nghe ta nói gì lần trước không vậy?</t>
+          <t>...Cậu có nghe tao nói gì lần trước không vậy?</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Cậu gần như đã hồi phục rồi... Nhưng không có nghĩa là được phép chạy đi đâu! Lần trước ta nói gì cậu có nghe không hả?</t>
+          <t>Cậu gần như đã hồi phục rồi... Nhưng không có nghĩa là được phép chạy đi đâu! Lần trước tao nói gì cậu có nghe không hả?</t>
         </is>
       </c>
     </row>
@@ -32619,7 +32619,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Đồ nhãi—! Làm thêm trò như thế nữa là ta sẽ báo cáo với cố vấn của ngươi và thu hồi đặc quyền phòng thí nghiệm của ngươi ngay lập tức!</t>
+          <t>Đồ nhãi—! Làm thêm trò như thế nữa là tao sẽ báo cáo với cố vấn của mày và thu hồi đặc quyền phòng thí nghiệm của mày ngay lập tức!</t>
         </is>
       </c>
     </row>
